--- a/data/availability/projects/madinet-masr/taj-city.xlsx
+++ b/data/availability/projects/madinet-masr/taj-city.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for taj-city</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -804,7 +814,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1020,7 +1030,6 @@
       <c r="G3" t="n">
         <v>100</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1077,7 +1086,6 @@
       <c r="G4" t="n">
         <v>155</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1134,7 +1142,6 @@
       <c r="G5" t="n">
         <v>65</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1191,7 +1198,6 @@
       <c r="G6" t="n">
         <v>392</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1224,7 +1230,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Administrative Office</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1248,7 +1254,6 @@
       <c r="G7" t="n">
         <v>56</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
